--- a/resultados/third_review/20260907_data2024_most_recent_medication.xlsx
+++ b/resultados/third_review/20260907_data2024_most_recent_medication.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">most_recent_medications</t>
   </si>
@@ -26,40 +26,85 @@
     <t xml:space="preserve">OCTREOTIDE LAR 30 MG INJECTABLE</t>
   </si>
   <si>
+    <t xml:space="preserve">OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">OCTREOTIDE LAR 20 MG INJECTABLE</t>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">LANREOTIDE 90 MG INJECTABLE</t>
   </si>
   <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
     <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">LANREOTIDE 60 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE</t>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 90 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 10 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 60 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 20 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">OCTREOTIDE 0.1 MG/ML INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 20 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 60 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CABERGOLINE 0.5 MG + OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 30 MG INJECTABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 60 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">LANREOTIDE 90 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
   </si>
   <si>
-    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + LANREOTIDE 90 MG INJECTABLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANREOTIDE 120 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
+    <t xml:space="preserve">OCTREOTIDE LAR 10 MG INJECTABLE + OCTREOTIDE LAR 20 MG INJECTABLE</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -404,7 +449,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>1785</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +457,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>729</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4">
@@ -420,7 +465,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>664</v>
+        <v>623</v>
       </c>
     </row>
     <row r="5">
@@ -428,7 +473,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>663</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6">
@@ -436,7 +481,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>264</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7">
@@ -444,7 +489,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
@@ -452,7 +497,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>39</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9">
@@ -460,7 +505,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -468,7 +513,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
@@ -476,7 +521,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -484,7 +529,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -492,7 +537,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -500,7 +545,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -508,7 +553,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -516,6 +561,126 @@
         <v>16</v>
       </c>
       <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="n">
         <v>4231</v>
       </c>
     </row>
